--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,6 +806,1038 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Projekt Östergötlands flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123156572</v>
+      </c>
+      <c r="B3" t="n">
+        <v>109250</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>524373</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6459662</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123156582</v>
+      </c>
+      <c r="B4" t="n">
+        <v>44690</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zygaena osterodensis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>524330</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6459764</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123156577</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98388</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>524344</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6459746</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123156573</v>
+      </c>
+      <c r="B6" t="n">
+        <v>109041</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>524365</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6459702</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123156579</v>
+      </c>
+      <c r="B7" t="n">
+        <v>109250</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>524340</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6459757</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123156574</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98388</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>524359</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6459720</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123156578</v>
+      </c>
+      <c r="B9" t="n">
+        <v>109041</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>524340</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6459749</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, stödremsan</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123156581</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98388</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>524338</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6459752</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123156575</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98388</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>524356</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6459728</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156572</v>
+        <v>123156581</v>
       </c>
       <c r="B3" t="n">
-        <v>109250</v>
+        <v>98388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,38 +823,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524373</v>
+        <v>524338</v>
       </c>
       <c r="R3" t="n">
-        <v>6459662</v>
+        <v>6459752</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -911,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -922,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156582</v>
+        <v>123178419</v>
       </c>
       <c r="B4" t="n">
-        <v>44690</v>
+        <v>109041</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,26 +942,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102020</v>
+        <v>220228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524330</v>
+        <v>524294</v>
       </c>
       <c r="R4" t="n">
-        <v>6459764</v>
+        <v>6459795</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1030,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1037,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156577</v>
+        <v>123156578</v>
       </c>
       <c r="B5" t="n">
-        <v>98388</v>
+        <v>109041</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,30 +1053,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1081,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524344</v>
+        <v>524340</v>
       </c>
       <c r="R5" t="n">
-        <v>6459746</v>
+        <v>6459749</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1145,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1152,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156573</v>
+        <v>123156575</v>
       </c>
       <c r="B6" t="n">
-        <v>109041</v>
+        <v>98388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,35 +1168,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1201,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524365</v>
+        <v>524356</v>
       </c>
       <c r="R6" t="n">
-        <v>6459702</v>
+        <v>6459728</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1261,7 +1260,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1272,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156579</v>
+        <v>123156577</v>
       </c>
       <c r="B7" t="n">
-        <v>109250</v>
+        <v>98388</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,38 +1283,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524340</v>
+        <v>524344</v>
       </c>
       <c r="R7" t="n">
-        <v>6459757</v>
+        <v>6459746</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1375,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1383,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156574</v>
+        <v>123178421</v>
       </c>
       <c r="B8" t="n">
-        <v>98388</v>
+        <v>109250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,30 +1398,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1427,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524359</v>
+        <v>524286</v>
       </c>
       <c r="R8" t="n">
-        <v>6459720</v>
+        <v>6459803</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1487,7 +1490,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1498,7 +1501,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123156578</v>
+        <v>123156573</v>
       </c>
       <c r="B9" t="n">
         <v>109041</v>
@@ -1533,7 +1536,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1542,10 +1550,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524340</v>
+        <v>524365</v>
       </c>
       <c r="R9" t="n">
-        <v>6459749</v>
+        <v>6459702</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1582,7 +1590,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,7 +1610,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1613,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156581</v>
+        <v>123156579</v>
       </c>
       <c r="B10" t="n">
-        <v>98388</v>
+        <v>109250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,42 +1633,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524338</v>
+        <v>524340</v>
       </c>
       <c r="R10" t="n">
-        <v>6459752</v>
+        <v>6459757</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1697,7 +1701,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,7 +1721,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1728,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123156575</v>
+        <v>123156572</v>
       </c>
       <c r="B11" t="n">
-        <v>98388</v>
+        <v>109250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,42 +1744,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524356</v>
+        <v>524373</v>
       </c>
       <c r="R11" t="n">
-        <v>6459728</v>
+        <v>6459662</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,10 +1832,355 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123178417</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98388</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>524302</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6459787</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, hela vägområdet</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Melina Eberhagen</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123156574</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98388</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>524359</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6459720</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123156582</v>
+      </c>
+      <c r="B14" t="n">
+        <v>44690</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102020</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Zygaena osterodensis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sjöhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>524330</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6459764</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156581</v>
+        <v>123178419</v>
       </c>
       <c r="B3" t="n">
-        <v>98388</v>
+        <v>109041</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,30 +823,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524338</v>
+        <v>524294</v>
       </c>
       <c r="R3" t="n">
-        <v>6459752</v>
+        <v>6459795</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,7 +926,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178419</v>
+        <v>123156573</v>
       </c>
       <c r="B4" t="n">
         <v>109041</v>
@@ -961,7 +961,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -970,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524294</v>
+        <v>524365</v>
       </c>
       <c r="R4" t="n">
-        <v>6459795</v>
+        <v>6459702</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,7 +1015,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156578</v>
+        <v>123178417</v>
       </c>
       <c r="B5" t="n">
-        <v>109041</v>
+        <v>98388</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,30 +1058,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524340</v>
+        <v>524302</v>
       </c>
       <c r="R5" t="n">
-        <v>6459749</v>
+        <v>6459787</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1125,7 +1130,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,7 +1161,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156575</v>
+        <v>123156577</v>
       </c>
       <c r="B6" t="n">
         <v>98388</v>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524356</v>
+        <v>524344</v>
       </c>
       <c r="R6" t="n">
-        <v>6459728</v>
+        <v>6459746</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1245,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156577</v>
+        <v>123156578</v>
       </c>
       <c r="B7" t="n">
-        <v>98388</v>
+        <v>109041</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,30 +1288,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524344</v>
+        <v>524340</v>
       </c>
       <c r="R7" t="n">
-        <v>6459746</v>
+        <v>6459749</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1355,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123178421</v>
+        <v>123156575</v>
       </c>
       <c r="B8" t="n">
-        <v>109250</v>
+        <v>98388</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,30 +1403,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1430,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524286</v>
+        <v>524356</v>
       </c>
       <c r="R8" t="n">
-        <v>6459803</v>
+        <v>6459728</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123156573</v>
+        <v>123178421</v>
       </c>
       <c r="B9" t="n">
-        <v>109041</v>
+        <v>109250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,16 +1522,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1536,12 +1541,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524365</v>
+        <v>524286</v>
       </c>
       <c r="R9" t="n">
-        <v>6459702</v>
+        <v>6459803</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156579</v>
+        <v>123156574</v>
       </c>
       <c r="B10" t="n">
-        <v>109250</v>
+        <v>98388</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,38 +1633,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524340</v>
+        <v>524359</v>
       </c>
       <c r="R10" t="n">
-        <v>6459757</v>
+        <v>6459720</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1732,7 +1736,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123156572</v>
+        <v>123156579</v>
       </c>
       <c r="B11" t="n">
         <v>109250</v>
@@ -1772,10 +1776,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524373</v>
+        <v>524340</v>
       </c>
       <c r="R11" t="n">
-        <v>6459662</v>
+        <v>6459757</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1812,7 +1816,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123178417</v>
+        <v>123156572</v>
       </c>
       <c r="B12" t="n">
-        <v>98388</v>
+        <v>109250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,42 +1859,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524302</v>
+        <v>524373</v>
       </c>
       <c r="R12" t="n">
-        <v>6459787</v>
+        <v>6459662</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,7 +1958,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123156574</v>
+        <v>123156581</v>
       </c>
       <c r="B13" t="n">
         <v>98388</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524359</v>
+        <v>524338</v>
       </c>
       <c r="R13" t="n">
-        <v>6459720</v>
+        <v>6459752</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,7 +811,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123178419</v>
+        <v>123156578</v>
       </c>
       <c r="B3" t="n">
         <v>109041</v>
@@ -846,7 +846,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524294</v>
+        <v>524340</v>
       </c>
       <c r="R3" t="n">
-        <v>6459795</v>
+        <v>6459749</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123178417</v>
+        <v>123156582</v>
       </c>
       <c r="B5" t="n">
-        <v>98388</v>
+        <v>44690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,30 +1058,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>102020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524302</v>
+        <v>524330</v>
       </c>
       <c r="R5" t="n">
-        <v>6459787</v>
+        <v>6459764</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1161,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156577</v>
+        <v>123178417</v>
       </c>
       <c r="B6" t="n">
         <v>98388</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524344</v>
+        <v>524302</v>
       </c>
       <c r="R6" t="n">
-        <v>6459746</v>
+        <v>6459787</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,7 +1276,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156578</v>
+        <v>123178419</v>
       </c>
       <c r="B7" t="n">
         <v>109041</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524340</v>
+        <v>524294</v>
       </c>
       <c r="R7" t="n">
-        <v>6459749</v>
+        <v>6459795</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,7 +1391,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156575</v>
+        <v>123156577</v>
       </c>
       <c r="B8" t="n">
         <v>98388</v>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524356</v>
+        <v>524344</v>
       </c>
       <c r="R8" t="n">
-        <v>6459728</v>
+        <v>6459746</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,7 +1506,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123178421</v>
+        <v>123156572</v>
       </c>
       <c r="B9" t="n">
         <v>109250</v>
@@ -1539,21 +1539,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524286</v>
+        <v>524373</v>
       </c>
       <c r="R9" t="n">
-        <v>6459803</v>
+        <v>6459662</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1590,7 +1586,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1617,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156574</v>
+        <v>123156579</v>
       </c>
       <c r="B10" t="n">
-        <v>98388</v>
+        <v>109250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,42 +1629,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524359</v>
+        <v>524340</v>
       </c>
       <c r="R10" t="n">
-        <v>6459720</v>
+        <v>6459757</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1736,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123156579</v>
+        <v>123156575</v>
       </c>
       <c r="B11" t="n">
-        <v>109250</v>
+        <v>98388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,38 +1740,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524340</v>
+        <v>524356</v>
       </c>
       <c r="R11" t="n">
-        <v>6459757</v>
+        <v>6459728</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1847,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123156572</v>
+        <v>123156581</v>
       </c>
       <c r="B12" t="n">
-        <v>109250</v>
+        <v>98388</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,38 +1855,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524373</v>
+        <v>524338</v>
       </c>
       <c r="R12" t="n">
-        <v>6459662</v>
+        <v>6459752</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1958,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123156581</v>
+        <v>123178421</v>
       </c>
       <c r="B13" t="n">
-        <v>98388</v>
+        <v>109250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,30 +1970,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524338</v>
+        <v>524286</v>
       </c>
       <c r="R13" t="n">
-        <v>6459752</v>
+        <v>6459803</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123156582</v>
+        <v>123156574</v>
       </c>
       <c r="B14" t="n">
-        <v>44690</v>
+        <v>98388</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,30 +2085,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102020</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524330</v>
+        <v>524359</v>
       </c>
       <c r="R14" t="n">
-        <v>6459764</v>
+        <v>6459720</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156578</v>
+        <v>123156579</v>
       </c>
       <c r="B3" t="n">
-        <v>109041</v>
+        <v>109250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,16 +827,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -844,11 +844,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
@@ -858,7 +854,7 @@
         <v>524340</v>
       </c>
       <c r="R3" t="n">
-        <v>6459749</v>
+        <v>6459757</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,7 +891,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156573</v>
+        <v>123156574</v>
       </c>
       <c r="B4" t="n">
-        <v>109041</v>
+        <v>98388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,35 +934,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -975,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524365</v>
+        <v>524359</v>
       </c>
       <c r="R4" t="n">
-        <v>6459702</v>
+        <v>6459720</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1046,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156582</v>
+        <v>123156573</v>
       </c>
       <c r="B5" t="n">
-        <v>44690</v>
+        <v>109041</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,26 +1053,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102020</v>
+        <v>220228</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1090,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524330</v>
+        <v>524365</v>
       </c>
       <c r="R5" t="n">
-        <v>6459764</v>
+        <v>6459702</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1161,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123178417</v>
+        <v>123156581</v>
       </c>
       <c r="B6" t="n">
         <v>98388</v>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1205,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524302</v>
+        <v>524338</v>
       </c>
       <c r="R6" t="n">
-        <v>6459787</v>
+        <v>6459752</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1245,7 +1241,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123178419</v>
+        <v>123156572</v>
       </c>
       <c r="B7" t="n">
-        <v>109041</v>
+        <v>109250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,16 +1288,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1309,21 +1305,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524294</v>
+        <v>524373</v>
       </c>
       <c r="R7" t="n">
-        <v>6459795</v>
+        <v>6459662</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,7 +1352,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1506,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123156572</v>
+        <v>123156575</v>
       </c>
       <c r="B9" t="n">
-        <v>109250</v>
+        <v>98388</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,38 +1510,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524373</v>
+        <v>524356</v>
       </c>
       <c r="R9" t="n">
-        <v>6459662</v>
+        <v>6459728</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,7 +1582,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156579</v>
+        <v>123156578</v>
       </c>
       <c r="B10" t="n">
-        <v>109250</v>
+        <v>109041</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,16 +1629,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1650,7 +1646,11 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
@@ -1660,7 +1660,7 @@
         <v>524340</v>
       </c>
       <c r="R10" t="n">
-        <v>6459757</v>
+        <v>6459749</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,7 +1728,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123156575</v>
+        <v>123178417</v>
       </c>
       <c r="B11" t="n">
         <v>98388</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524356</v>
+        <v>524302</v>
       </c>
       <c r="R11" t="n">
-        <v>6459728</v>
+        <v>6459787</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123156581</v>
+        <v>123178421</v>
       </c>
       <c r="B12" t="n">
-        <v>98388</v>
+        <v>109250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,30 +1855,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524338</v>
+        <v>524286</v>
       </c>
       <c r="R12" t="n">
-        <v>6459752</v>
+        <v>6459803</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123178421</v>
+        <v>123156582</v>
       </c>
       <c r="B13" t="n">
-        <v>109250</v>
+        <v>44690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,26 +1974,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>102020</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524286</v>
+        <v>524330</v>
       </c>
       <c r="R13" t="n">
-        <v>6459803</v>
+        <v>6459764</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123156574</v>
+        <v>123178419</v>
       </c>
       <c r="B14" t="n">
-        <v>98388</v>
+        <v>109041</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,30 +2085,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524359</v>
+        <v>524294</v>
       </c>
       <c r="R14" t="n">
-        <v>6459720</v>
+        <v>6459795</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156579</v>
+        <v>123156581</v>
       </c>
       <c r="B3" t="n">
-        <v>109250</v>
+        <v>98391</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,38 +823,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524340</v>
+        <v>524338</v>
       </c>
       <c r="R3" t="n">
-        <v>6459757</v>
+        <v>6459752</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156574</v>
+        <v>123156578</v>
       </c>
       <c r="B4" t="n">
-        <v>98388</v>
+        <v>109045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,25 +938,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -966,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524359</v>
+        <v>524340</v>
       </c>
       <c r="R4" t="n">
-        <v>6459720</v>
+        <v>6459749</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156573</v>
+        <v>123156577</v>
       </c>
       <c r="B5" t="n">
-        <v>109041</v>
+        <v>98391</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,35 +1053,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524365</v>
+        <v>524344</v>
       </c>
       <c r="R5" t="n">
-        <v>6459702</v>
+        <v>6459746</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156581</v>
+        <v>123156573</v>
       </c>
       <c r="B6" t="n">
-        <v>98388</v>
+        <v>109045</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,30 +1168,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1201,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524338</v>
+        <v>524365</v>
       </c>
       <c r="R6" t="n">
-        <v>6459752</v>
+        <v>6459702</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1241,7 +1245,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156572</v>
+        <v>123178421</v>
       </c>
       <c r="B7" t="n">
-        <v>109250</v>
+        <v>109254</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,17 +1309,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524373</v>
+        <v>524286</v>
       </c>
       <c r="R7" t="n">
-        <v>6459662</v>
+        <v>6459803</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156577</v>
+        <v>123156579</v>
       </c>
       <c r="B8" t="n">
-        <v>98388</v>
+        <v>109254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,42 +1403,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524344</v>
+        <v>524340</v>
       </c>
       <c r="R8" t="n">
-        <v>6459746</v>
+        <v>6459757</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1467,7 +1471,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123156575</v>
+        <v>123178417</v>
       </c>
       <c r="B9" t="n">
-        <v>98388</v>
+        <v>98391</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,7 +1537,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1542,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524356</v>
+        <v>524302</v>
       </c>
       <c r="R9" t="n">
-        <v>6459728</v>
+        <v>6459787</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1582,7 +1586,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1617,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156578</v>
+        <v>123156572</v>
       </c>
       <c r="B10" t="n">
-        <v>109041</v>
+        <v>109254</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,16 +1633,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1646,21 +1650,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524340</v>
+        <v>524373</v>
       </c>
       <c r="R10" t="n">
-        <v>6459749</v>
+        <v>6459662</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123178417</v>
+        <v>123156582</v>
       </c>
       <c r="B11" t="n">
-        <v>98388</v>
+        <v>44693</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,30 +1740,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>102020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524302</v>
+        <v>524330</v>
       </c>
       <c r="R11" t="n">
-        <v>6459787</v>
+        <v>6459764</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123178421</v>
+        <v>123156574</v>
       </c>
       <c r="B12" t="n">
-        <v>109250</v>
+        <v>98391</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,30 +1855,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524286</v>
+        <v>524359</v>
       </c>
       <c r="R12" t="n">
-        <v>6459803</v>
+        <v>6459720</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1958,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123156582</v>
+        <v>123178419</v>
       </c>
       <c r="B13" t="n">
-        <v>44690</v>
+        <v>109045</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,26 +1974,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102020</v>
+        <v>220228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524330</v>
+        <v>524294</v>
       </c>
       <c r="R13" t="n">
-        <v>6459764</v>
+        <v>6459795</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123178419</v>
+        <v>123156575</v>
       </c>
       <c r="B14" t="n">
-        <v>109041</v>
+        <v>98391</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,30 +2085,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524294</v>
+        <v>524356</v>
       </c>
       <c r="R14" t="n">
-        <v>6459795</v>
+        <v>6459728</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156581</v>
+        <v>123156578</v>
       </c>
       <c r="B3" t="n">
-        <v>98391</v>
+        <v>109047</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,30 +823,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524338</v>
+        <v>524340</v>
       </c>
       <c r="R3" t="n">
-        <v>6459752</v>
+        <v>6459749</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156578</v>
+        <v>123156582</v>
       </c>
       <c r="B4" t="n">
-        <v>109045</v>
+        <v>44693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,26 +942,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524340</v>
+        <v>524330</v>
       </c>
       <c r="R4" t="n">
-        <v>6459749</v>
+        <v>6459764</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156577</v>
+        <v>123178419</v>
       </c>
       <c r="B5" t="n">
-        <v>98391</v>
+        <v>109047</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,30 +1053,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524344</v>
+        <v>524294</v>
       </c>
       <c r="R5" t="n">
-        <v>6459746</v>
+        <v>6459795</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156573</v>
+        <v>123156575</v>
       </c>
       <c r="B6" t="n">
-        <v>109045</v>
+        <v>98393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,35 +1168,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524365</v>
+        <v>524356</v>
       </c>
       <c r="R6" t="n">
-        <v>6459702</v>
+        <v>6459728</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1276,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123178421</v>
+        <v>123156573</v>
       </c>
       <c r="B7" t="n">
-        <v>109254</v>
+        <v>109047</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,16 +1287,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1311,7 +1306,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524286</v>
+        <v>524365</v>
       </c>
       <c r="R7" t="n">
-        <v>6459803</v>
+        <v>6459702</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156579</v>
+        <v>123156574</v>
       </c>
       <c r="B8" t="n">
-        <v>109254</v>
+        <v>98393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,38 +1403,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524340</v>
+        <v>524359</v>
       </c>
       <c r="R8" t="n">
-        <v>6459757</v>
+        <v>6459720</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1502,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123178417</v>
+        <v>123156579</v>
       </c>
       <c r="B9" t="n">
-        <v>98391</v>
+        <v>109256</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,42 +1518,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524302</v>
+        <v>524340</v>
       </c>
       <c r="R9" t="n">
-        <v>6459787</v>
+        <v>6459757</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,10 +1617,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156572</v>
+        <v>123156577</v>
       </c>
       <c r="B10" t="n">
-        <v>109254</v>
+        <v>98393</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,38 +1629,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524373</v>
+        <v>524344</v>
       </c>
       <c r="R10" t="n">
-        <v>6459662</v>
+        <v>6459746</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1728,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123156582</v>
+        <v>123156581</v>
       </c>
       <c r="B11" t="n">
-        <v>44693</v>
+        <v>98393</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,25 +1744,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102020</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1772,10 +1776,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524330</v>
+        <v>524338</v>
       </c>
       <c r="R11" t="n">
-        <v>6459764</v>
+        <v>6459752</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1812,7 +1816,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123156574</v>
+        <v>123178421</v>
       </c>
       <c r="B12" t="n">
-        <v>98391</v>
+        <v>109256</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,30 +1859,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1887,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524359</v>
+        <v>524286</v>
       </c>
       <c r="R12" t="n">
-        <v>6459720</v>
+        <v>6459803</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1958,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123178419</v>
+        <v>123156572</v>
       </c>
       <c r="B13" t="n">
-        <v>109045</v>
+        <v>109256</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,16 +1978,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1991,21 +1995,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524294</v>
+        <v>524373</v>
       </c>
       <c r="R13" t="n">
-        <v>6459795</v>
+        <v>6459662</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123156575</v>
+        <v>123178417</v>
       </c>
       <c r="B14" t="n">
-        <v>98391</v>
+        <v>98393</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524356</v>
+        <v>524302</v>
       </c>
       <c r="R14" t="n">
-        <v>6459728</v>
+        <v>6459787</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156578</v>
+        <v>123156575</v>
       </c>
       <c r="B3" t="n">
-        <v>109047</v>
+        <v>98399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,30 +823,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524340</v>
+        <v>524356</v>
       </c>
       <c r="R3" t="n">
-        <v>6459749</v>
+        <v>6459728</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156582</v>
+        <v>123178421</v>
       </c>
       <c r="B4" t="n">
-        <v>44693</v>
+        <v>109262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,26 +942,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102020</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524330</v>
+        <v>524286</v>
       </c>
       <c r="R4" t="n">
-        <v>6459764</v>
+        <v>6459803</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123178419</v>
+        <v>123156579</v>
       </c>
       <c r="B5" t="n">
-        <v>109047</v>
+        <v>109262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,16 +1057,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1074,21 +1074,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524294</v>
+        <v>524340</v>
       </c>
       <c r="R5" t="n">
-        <v>6459795</v>
+        <v>6459757</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1125,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156575</v>
+        <v>123178417</v>
       </c>
       <c r="B6" t="n">
-        <v>98393</v>
+        <v>98399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524356</v>
+        <v>524302</v>
       </c>
       <c r="R6" t="n">
-        <v>6459728</v>
+        <v>6459787</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156573</v>
+        <v>123156574</v>
       </c>
       <c r="B7" t="n">
-        <v>109047</v>
+        <v>98399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,35 +1279,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524365</v>
+        <v>524359</v>
       </c>
       <c r="R7" t="n">
-        <v>6459702</v>
+        <v>6459720</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1391,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156574</v>
+        <v>123156573</v>
       </c>
       <c r="B8" t="n">
-        <v>98393</v>
+        <v>109053</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,30 +1394,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1435,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524359</v>
+        <v>524365</v>
       </c>
       <c r="R8" t="n">
-        <v>6459720</v>
+        <v>6459702</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1506,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123156579</v>
+        <v>123156577</v>
       </c>
       <c r="B9" t="n">
-        <v>109256</v>
+        <v>98399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,38 +1514,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524340</v>
+        <v>524344</v>
       </c>
       <c r="R9" t="n">
-        <v>6459757</v>
+        <v>6459746</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,10 +1617,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156577</v>
+        <v>123156572</v>
       </c>
       <c r="B10" t="n">
-        <v>98393</v>
+        <v>109262</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,42 +1629,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524344</v>
+        <v>524373</v>
       </c>
       <c r="R10" t="n">
-        <v>6459746</v>
+        <v>6459662</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1732,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123156581</v>
+        <v>123156578</v>
       </c>
       <c r="B11" t="n">
-        <v>98393</v>
+        <v>109053</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,30 +1740,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1776,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524338</v>
+        <v>524340</v>
       </c>
       <c r="R11" t="n">
-        <v>6459752</v>
+        <v>6459749</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1816,7 +1812,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123178421</v>
+        <v>123156581</v>
       </c>
       <c r="B12" t="n">
-        <v>109256</v>
+        <v>98399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,30 +1855,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1891,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524286</v>
+        <v>524338</v>
       </c>
       <c r="R12" t="n">
-        <v>6459803</v>
+        <v>6459752</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1931,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123156572</v>
+        <v>123178419</v>
       </c>
       <c r="B13" t="n">
-        <v>109256</v>
+        <v>109053</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,16 +1974,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1995,17 +1991,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524373</v>
+        <v>524294</v>
       </c>
       <c r="R13" t="n">
-        <v>6459662</v>
+        <v>6459795</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123178417</v>
+        <v>123156582</v>
       </c>
       <c r="B14" t="n">
-        <v>98393</v>
+        <v>44693</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,30 +2085,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>102020</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524302</v>
+        <v>524330</v>
       </c>
       <c r="R14" t="n">
-        <v>6459787</v>
+        <v>6459764</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156575</v>
+        <v>123178417</v>
       </c>
       <c r="B3" t="n">
-        <v>98399</v>
+        <v>98402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524356</v>
+        <v>524302</v>
       </c>
       <c r="R3" t="n">
-        <v>6459728</v>
+        <v>6459787</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178421</v>
+        <v>123156578</v>
       </c>
       <c r="B4" t="n">
-        <v>109262</v>
+        <v>109056</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,16 +942,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524286</v>
+        <v>524340</v>
       </c>
       <c r="R4" t="n">
-        <v>6459803</v>
+        <v>6459749</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156579</v>
+        <v>123156574</v>
       </c>
       <c r="B5" t="n">
-        <v>109262</v>
+        <v>98402</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,38 +1053,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524340</v>
+        <v>524359</v>
       </c>
       <c r="R5" t="n">
-        <v>6459757</v>
+        <v>6459720</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1152,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123178417</v>
+        <v>123178421</v>
       </c>
       <c r="B6" t="n">
-        <v>98399</v>
+        <v>109265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,30 +1168,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1196,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524302</v>
+        <v>524286</v>
       </c>
       <c r="R6" t="n">
-        <v>6459787</v>
+        <v>6459803</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1236,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156574</v>
+        <v>123156581</v>
       </c>
       <c r="B7" t="n">
-        <v>98399</v>
+        <v>98402</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,7 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524359</v>
+        <v>524338</v>
       </c>
       <c r="R7" t="n">
-        <v>6459720</v>
+        <v>6459752</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156573</v>
+        <v>123178419</v>
       </c>
       <c r="B8" t="n">
-        <v>109053</v>
+        <v>109056</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,12 +1421,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1431,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524365</v>
+        <v>524294</v>
       </c>
       <c r="R8" t="n">
-        <v>6459702</v>
+        <v>6459795</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123156577</v>
+        <v>123156582</v>
       </c>
       <c r="B9" t="n">
-        <v>98399</v>
+        <v>44693</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,25 +1513,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>102020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1546,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524344</v>
+        <v>524330</v>
       </c>
       <c r="R9" t="n">
-        <v>6459746</v>
+        <v>6459764</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156572</v>
+        <v>123156573</v>
       </c>
       <c r="B10" t="n">
-        <v>109262</v>
+        <v>109056</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,16 +1632,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1650,17 +1649,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524373</v>
+        <v>524365</v>
       </c>
       <c r="R10" t="n">
-        <v>6459662</v>
+        <v>6459702</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1697,7 +1705,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123156578</v>
+        <v>123156577</v>
       </c>
       <c r="B11" t="n">
-        <v>109053</v>
+        <v>98402</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,30 +1748,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1772,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524340</v>
+        <v>524344</v>
       </c>
       <c r="R11" t="n">
-        <v>6459749</v>
+        <v>6459746</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1812,7 +1820,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123156581</v>
+        <v>123156572</v>
       </c>
       <c r="B12" t="n">
-        <v>98399</v>
+        <v>109265</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,42 +1863,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524338</v>
+        <v>524373</v>
       </c>
       <c r="R12" t="n">
-        <v>6459752</v>
+        <v>6459662</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1958,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123178419</v>
+        <v>123156579</v>
       </c>
       <c r="B13" t="n">
-        <v>109053</v>
+        <v>109265</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,16 +1978,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1991,21 +1995,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524294</v>
+        <v>524340</v>
       </c>
       <c r="R13" t="n">
-        <v>6459795</v>
+        <v>6459757</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123156582</v>
+        <v>123156575</v>
       </c>
       <c r="B14" t="n">
-        <v>44693</v>
+        <v>98402</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102020</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524330</v>
+        <v>524356</v>
       </c>
       <c r="R14" t="n">
-        <v>6459764</v>
+        <v>6459728</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123178417</v>
+        <v>123178421</v>
       </c>
       <c r="B3" t="n">
-        <v>98402</v>
+        <v>109282</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,30 +823,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524302</v>
+        <v>524286</v>
       </c>
       <c r="R3" t="n">
-        <v>6459787</v>
+        <v>6459803</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156578</v>
+        <v>123178419</v>
       </c>
       <c r="B4" t="n">
-        <v>109056</v>
+        <v>109073</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524340</v>
+        <v>524294</v>
       </c>
       <c r="R4" t="n">
-        <v>6459749</v>
+        <v>6459795</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156574</v>
+        <v>123156575</v>
       </c>
       <c r="B5" t="n">
-        <v>98402</v>
+        <v>98419</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524359</v>
+        <v>524356</v>
       </c>
       <c r="R5" t="n">
-        <v>6459720</v>
+        <v>6459728</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123178421</v>
+        <v>123156574</v>
       </c>
       <c r="B6" t="n">
-        <v>109265</v>
+        <v>98419</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,30 +1168,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524286</v>
+        <v>524359</v>
       </c>
       <c r="R6" t="n">
-        <v>6459803</v>
+        <v>6459720</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156581</v>
+        <v>123156573</v>
       </c>
       <c r="B7" t="n">
-        <v>98402</v>
+        <v>109073</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,30 +1283,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524338</v>
+        <v>524365</v>
       </c>
       <c r="R7" t="n">
-        <v>6459752</v>
+        <v>6459702</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1355,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123178419</v>
+        <v>123156582</v>
       </c>
       <c r="B8" t="n">
-        <v>109056</v>
+        <v>44699</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,26 +1407,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1430,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524294</v>
+        <v>524330</v>
       </c>
       <c r="R8" t="n">
-        <v>6459795</v>
+        <v>6459764</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,7 +1475,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123156582</v>
+        <v>123156581</v>
       </c>
       <c r="B9" t="n">
-        <v>44693</v>
+        <v>98419</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,25 +1518,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102020</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1545,10 +1550,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524330</v>
+        <v>524338</v>
       </c>
       <c r="R9" t="n">
-        <v>6459764</v>
+        <v>6459752</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1585,7 +1590,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156573</v>
+        <v>123156578</v>
       </c>
       <c r="B10" t="n">
-        <v>109056</v>
+        <v>109073</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,12 +1656,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524365</v>
+        <v>524340</v>
       </c>
       <c r="R10" t="n">
-        <v>6459702</v>
+        <v>6459749</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,7 +1739,7 @@
         <v>123156577</v>
       </c>
       <c r="B11" t="n">
-        <v>98402</v>
+        <v>98419</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123156572</v>
+        <v>123156579</v>
       </c>
       <c r="B12" t="n">
-        <v>109265</v>
+        <v>109282</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524373</v>
+        <v>524340</v>
       </c>
       <c r="R12" t="n">
-        <v>6459662</v>
+        <v>6459757</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123156579</v>
+        <v>123156572</v>
       </c>
       <c r="B13" t="n">
-        <v>109265</v>
+        <v>109282</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524340</v>
+        <v>524373</v>
       </c>
       <c r="R13" t="n">
-        <v>6459757</v>
+        <v>6459662</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123156575</v>
+        <v>123178417</v>
       </c>
       <c r="B14" t="n">
-        <v>98402</v>
+        <v>98419</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524356</v>
+        <v>524302</v>
       </c>
       <c r="R14" t="n">
-        <v>6459728</v>
+        <v>6459787</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123178421</v>
+        <v>123156572</v>
       </c>
       <c r="B3" t="n">
-        <v>109282</v>
+        <v>109300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -844,21 +844,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524286</v>
+        <v>524373</v>
       </c>
       <c r="R3" t="n">
-        <v>6459803</v>
+        <v>6459662</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,7 +891,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178419</v>
+        <v>123156582</v>
       </c>
       <c r="B4" t="n">
-        <v>109073</v>
+        <v>44702</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,26 +938,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -970,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524294</v>
+        <v>524330</v>
       </c>
       <c r="R4" t="n">
-        <v>6459795</v>
+        <v>6459764</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,7 +1006,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156575</v>
+        <v>123178419</v>
       </c>
       <c r="B5" t="n">
-        <v>98419</v>
+        <v>109091</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,30 +1049,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524356</v>
+        <v>524294</v>
       </c>
       <c r="R5" t="n">
-        <v>6459728</v>
+        <v>6459795</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1125,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156574</v>
+        <v>123156573</v>
       </c>
       <c r="B6" t="n">
-        <v>98419</v>
+        <v>109091</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,30 +1164,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524359</v>
+        <v>524365</v>
       </c>
       <c r="R6" t="n">
-        <v>6459720</v>
+        <v>6459702</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1271,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156573</v>
+        <v>123156578</v>
       </c>
       <c r="B7" t="n">
-        <v>109073</v>
+        <v>109091</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,12 +1307,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524365</v>
+        <v>524340</v>
       </c>
       <c r="R7" t="n">
-        <v>6459702</v>
+        <v>6459749</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,7 +1356,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156582</v>
+        <v>123156581</v>
       </c>
       <c r="B8" t="n">
-        <v>44699</v>
+        <v>98525</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,25 +1399,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102020</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1435,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524330</v>
+        <v>524338</v>
       </c>
       <c r="R8" t="n">
-        <v>6459764</v>
+        <v>6459752</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,7 +1471,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123156581</v>
+        <v>123156577</v>
       </c>
       <c r="B9" t="n">
-        <v>98419</v>
+        <v>98525</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524338</v>
+        <v>524344</v>
       </c>
       <c r="R9" t="n">
-        <v>6459752</v>
+        <v>6459746</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1621,10 +1617,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156578</v>
+        <v>123156574</v>
       </c>
       <c r="B10" t="n">
-        <v>109073</v>
+        <v>98525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,25 +1629,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1665,10 +1661,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524340</v>
+        <v>524359</v>
       </c>
       <c r="R10" t="n">
-        <v>6459749</v>
+        <v>6459720</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1705,7 +1701,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123156577</v>
+        <v>123178417</v>
       </c>
       <c r="B11" t="n">
-        <v>98419</v>
+        <v>98525</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,7 +1767,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1780,10 +1776,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524344</v>
+        <v>524302</v>
       </c>
       <c r="R11" t="n">
-        <v>6459746</v>
+        <v>6459787</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,7 +1816,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,7 +1850,7 @@
         <v>123156579</v>
       </c>
       <c r="B12" t="n">
-        <v>109282</v>
+        <v>109300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1962,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123156572</v>
+        <v>123178421</v>
       </c>
       <c r="B13" t="n">
-        <v>109282</v>
+        <v>109300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,17 +1991,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524373</v>
+        <v>524286</v>
       </c>
       <c r="R13" t="n">
-        <v>6459662</v>
+        <v>6459803</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123178417</v>
+        <v>123156575</v>
       </c>
       <c r="B14" t="n">
-        <v>98419</v>
+        <v>98525</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524302</v>
+        <v>524356</v>
       </c>
       <c r="R14" t="n">
-        <v>6459787</v>
+        <v>6459728</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156572</v>
+        <v>123156575</v>
       </c>
       <c r="B3" t="n">
-        <v>109300</v>
+        <v>98527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,38 +823,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524373</v>
+        <v>524356</v>
       </c>
       <c r="R3" t="n">
-        <v>6459662</v>
+        <v>6459728</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156582</v>
+        <v>123156579</v>
       </c>
       <c r="B4" t="n">
-        <v>44702</v>
+        <v>109302</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,38 +942,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102020</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524330</v>
+        <v>524340</v>
       </c>
       <c r="R4" t="n">
-        <v>6459764</v>
+        <v>6459757</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123178419</v>
+        <v>123156572</v>
       </c>
       <c r="B5" t="n">
-        <v>109091</v>
+        <v>109302</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1070,21 +1070,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524294</v>
+        <v>524373</v>
       </c>
       <c r="R5" t="n">
-        <v>6459795</v>
+        <v>6459662</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1117,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1151,7 @@
         <v>123156573</v>
       </c>
       <c r="B6" t="n">
-        <v>109091</v>
+        <v>109093</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1272,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156578</v>
+        <v>123178417</v>
       </c>
       <c r="B7" t="n">
-        <v>109091</v>
+        <v>98527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,30 +1280,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1316,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524340</v>
+        <v>524302</v>
       </c>
       <c r="R7" t="n">
-        <v>6459749</v>
+        <v>6459787</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,7 +1352,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123156581</v>
+        <v>123178421</v>
       </c>
       <c r="B8" t="n">
-        <v>98525</v>
+        <v>109302</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,30 +1395,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1431,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524338</v>
+        <v>524286</v>
       </c>
       <c r="R8" t="n">
-        <v>6459752</v>
+        <v>6459803</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,7 +1467,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123156577</v>
+        <v>123156581</v>
       </c>
       <c r="B9" t="n">
-        <v>98525</v>
+        <v>98527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,10 +1542,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524344</v>
+        <v>524338</v>
       </c>
       <c r="R9" t="n">
-        <v>6459746</v>
+        <v>6459752</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1617,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156574</v>
+        <v>123156582</v>
       </c>
       <c r="B10" t="n">
-        <v>98525</v>
+        <v>44702</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,30 +1625,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>102020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1661,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524359</v>
+        <v>524330</v>
       </c>
       <c r="R10" t="n">
-        <v>6459720</v>
+        <v>6459764</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1732,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123178417</v>
+        <v>123156578</v>
       </c>
       <c r="B11" t="n">
-        <v>98525</v>
+        <v>109093</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,30 +1740,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1776,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524302</v>
+        <v>524340</v>
       </c>
       <c r="R11" t="n">
-        <v>6459787</v>
+        <v>6459749</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1816,7 +1812,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123156579</v>
+        <v>123178419</v>
       </c>
       <c r="B12" t="n">
-        <v>109300</v>
+        <v>109093</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,16 +1859,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1880,17 +1876,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524340</v>
+        <v>524294</v>
       </c>
       <c r="R12" t="n">
-        <v>6459757</v>
+        <v>6459795</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123178421</v>
+        <v>123156577</v>
       </c>
       <c r="B13" t="n">
-        <v>109300</v>
+        <v>98527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,30 +1970,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524286</v>
+        <v>524344</v>
       </c>
       <c r="R13" t="n">
-        <v>6459803</v>
+        <v>6459746</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123156575</v>
+        <v>123156574</v>
       </c>
       <c r="B14" t="n">
-        <v>98525</v>
+        <v>98527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524356</v>
+        <v>524359</v>
       </c>
       <c r="R14" t="n">
-        <v>6459728</v>
+        <v>6459720</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123178419</v>
+        <v>123156577</v>
       </c>
       <c r="B12" t="n">
-        <v>109093</v>
+        <v>98527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,30 +1855,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524294</v>
+        <v>524344</v>
       </c>
       <c r="R12" t="n">
-        <v>6459795</v>
+        <v>6459746</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123156577</v>
+        <v>123178419</v>
       </c>
       <c r="B13" t="n">
-        <v>98527</v>
+        <v>109093</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,30 +1970,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524344</v>
+        <v>524294</v>
       </c>
       <c r="R13" t="n">
-        <v>6459746</v>
+        <v>6459795</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156579</v>
+        <v>123178417</v>
       </c>
       <c r="B4" t="n">
-        <v>109302</v>
+        <v>98527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,38 +938,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524340</v>
+        <v>524302</v>
       </c>
       <c r="R4" t="n">
-        <v>6459757</v>
+        <v>6459787</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156572</v>
+        <v>123156579</v>
       </c>
       <c r="B5" t="n">
         <v>109302</v>
@@ -1077,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524373</v>
+        <v>524340</v>
       </c>
       <c r="R5" t="n">
-        <v>6459662</v>
+        <v>6459757</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156573</v>
+        <v>123156572</v>
       </c>
       <c r="B6" t="n">
-        <v>109093</v>
+        <v>109302</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,16 +1168,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1181,26 +1185,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524365</v>
+        <v>524373</v>
       </c>
       <c r="R6" t="n">
-        <v>6459702</v>
+        <v>6459662</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1237,7 +1232,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123178417</v>
+        <v>123156573</v>
       </c>
       <c r="B7" t="n">
-        <v>98527</v>
+        <v>109093</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,30 +1275,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524302</v>
+        <v>524365</v>
       </c>
       <c r="R7" t="n">
-        <v>6459787</v>
+        <v>6459702</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123156577</v>
+        <v>123178419</v>
       </c>
       <c r="B12" t="n">
-        <v>98527</v>
+        <v>109093</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,30 +1855,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524344</v>
+        <v>524294</v>
       </c>
       <c r="R12" t="n">
-        <v>6459746</v>
+        <v>6459795</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123178419</v>
+        <v>123156577</v>
       </c>
       <c r="B13" t="n">
-        <v>109093</v>
+        <v>98527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,30 +1970,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524294</v>
+        <v>524344</v>
       </c>
       <c r="R13" t="n">
-        <v>6459795</v>
+        <v>6459746</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 38229-2023 artfynd.xlsx
+++ b/artfynd/A 38229-2023 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156575</v>
+        <v>123178421</v>
       </c>
       <c r="B3" t="n">
-        <v>98527</v>
+        <v>108877</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,30 +823,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524356</v>
+        <v>524286</v>
       </c>
       <c r="R3" t="n">
-        <v>6459728</v>
+        <v>6459803</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178417</v>
+        <v>123156577</v>
       </c>
       <c r="B4" t="n">
-        <v>98527</v>
+        <v>98102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524302</v>
+        <v>524344</v>
       </c>
       <c r="R4" t="n">
-        <v>6459787</v>
+        <v>6459746</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123156579</v>
+        <v>123156581</v>
       </c>
       <c r="B5" t="n">
-        <v>109302</v>
+        <v>98102</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,38 +1053,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524340</v>
+        <v>524338</v>
       </c>
       <c r="R5" t="n">
-        <v>6459757</v>
+        <v>6459752</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123156572</v>
+        <v>123178417</v>
       </c>
       <c r="B6" t="n">
-        <v>109302</v>
+        <v>98102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,38 +1168,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524373</v>
+        <v>524302</v>
       </c>
       <c r="R6" t="n">
-        <v>6459662</v>
+        <v>6459787</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123156573</v>
+        <v>123156575</v>
       </c>
       <c r="B7" t="n">
-        <v>109093</v>
+        <v>98102</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,35 +1283,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220228</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1312,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524365</v>
+        <v>524356</v>
       </c>
       <c r="R7" t="n">
-        <v>6459702</v>
+        <v>6459728</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1383,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123178421</v>
+        <v>123156573</v>
       </c>
       <c r="B8" t="n">
-        <v>109302</v>
+        <v>108668</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,16 +1402,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1418,7 +1421,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1427,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524286</v>
+        <v>524365</v>
       </c>
       <c r="R8" t="n">
-        <v>6459803</v>
+        <v>6459702</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1498,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123156581</v>
+        <v>123178419</v>
       </c>
       <c r="B9" t="n">
-        <v>98527</v>
+        <v>108668</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,30 +1518,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1542,10 +1550,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524338</v>
+        <v>524294</v>
       </c>
       <c r="R9" t="n">
-        <v>6459752</v>
+        <v>6459795</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1582,7 +1590,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123156582</v>
+        <v>123156574</v>
       </c>
       <c r="B10" t="n">
-        <v>44702</v>
+        <v>98102</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,30 +1633,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102020</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1657,10 +1665,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524330</v>
+        <v>524359</v>
       </c>
       <c r="R10" t="n">
-        <v>6459764</v>
+        <v>6459720</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1728,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123156578</v>
+        <v>123156579</v>
       </c>
       <c r="B11" t="n">
-        <v>109093</v>
+        <v>108877</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,16 +1752,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1761,11 +1769,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
@@ -1775,7 +1779,7 @@
         <v>524340</v>
       </c>
       <c r="R11" t="n">
-        <v>6459749</v>
+        <v>6459757</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1812,7 +1816,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Östra vägsidan, stödremsan</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123178419</v>
+        <v>123156572</v>
       </c>
       <c r="B12" t="n">
-        <v>109093</v>
+        <v>108877</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,16 +1863,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1876,21 +1880,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sjöhagen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524294</v>
+        <v>524373</v>
       </c>
       <c r="R12" t="n">
-        <v>6459795</v>
+        <v>6459662</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123156577</v>
+        <v>123156578</v>
       </c>
       <c r="B13" t="n">
-        <v>98527</v>
+        <v>108668</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,30 +1970,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>220228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524344</v>
+        <v>524340</v>
       </c>
       <c r="R13" t="n">
-        <v>6459746</v>
+        <v>6459749</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, stödremsan</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123156574</v>
+        <v>123156582</v>
       </c>
       <c r="B14" t="n">
-        <v>98527</v>
+        <v>44702</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,30 +2085,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>102020</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524359</v>
+        <v>524330</v>
       </c>
       <c r="R14" t="n">
-        <v>6459720</v>
+        <v>6459764</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
